--- a/data/Ammonia_paper/model_inputs/Data_ammonia_paper.xlsx
+++ b/data/Ammonia_paper/model_inputs/Data_ammonia_paper.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA624466-5CAF-4125-999B-B70E5CDA2366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6180" activeTab="3"/>
+    <workbookView xWindow="22932" yWindow="-1620" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_base_case" sheetId="79" r:id="rId1"/>
@@ -21,7 +22,7 @@
     <definedName name="CEPCI2015">[1]Calculations!$C$23</definedName>
     <definedName name="DE2014_">[1]Calculations!$C$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="155">
   <si>
     <t>Red: Don't change the name without changing the Julia code</t>
   </si>
@@ -329,15 +330,9 @@
     <t>Year data</t>
   </si>
   <si>
-    <t>Profile folder name</t>
-  </si>
-  <si>
     <t>Name of the excel file profile</t>
   </si>
   <si>
-    <t>Folder name where the excel profile is</t>
-  </si>
-  <si>
     <t>Investment (EUR/Capacity installed)</t>
   </si>
   <si>
@@ -378,9 +373,6 @@
   </si>
   <si>
     <t>Electrolysers AEC</t>
-  </si>
-  <si>
-    <t>All_locations</t>
   </si>
   <si>
     <t>Arica</t>
@@ -518,7 +510,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -728,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -835,30 +827,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -953,15 +930,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -975,31 +943,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -1039,457 +991,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="64">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1529,7 +1031,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sources"/>
@@ -1860,7 +1362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1872,9 +1374,9 @@
     <col min="5" max="5" width="7.1796875" style="9" customWidth="1"/>
     <col min="6" max="6" width="11.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.90625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" style="121" customWidth="1"/>
+    <col min="8" max="8" width="17.36328125" style="3" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" style="113" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" style="103" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
@@ -1894,26 +1396,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="130" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="131"/>
+      <c r="A1" s="114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="115"/>
       <c r="F1" s="44" t="s">
         <v>73</v>
       </c>
       <c r="G1" s="44" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H1" s="44" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I1" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="J1" s="110" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="100" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="45" t="s">
@@ -1947,33 +1449,33 @@
         <v>48</v>
       </c>
       <c r="U1" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="V1" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="W1" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="X1" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="V1" s="47" t="s">
+      <c r="Y1" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="W1" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="X1" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y1" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z1" s="50" t="s">
+      <c r="Z1" s="46" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="32"/>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="134" t="s">
+      <c r="C2" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="133" t="s">
+      <c r="D2" s="117" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="34" t="s">
@@ -2066,9 +1568,9 @@
     </row>
     <row r="3" spans="1:26" s="6" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="33"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="133"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="117"/>
       <c r="E3" s="34" t="s">
         <v>54</v>
       </c>
@@ -2084,7 +1586,7 @@
       <c r="I3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="111" t="s">
+      <c r="J3" s="101" t="s">
         <v>74</v>
       </c>
       <c r="K3" s="15" t="s">
@@ -2099,48 +1601,48 @@
       <c r="N3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="O3" s="48">
+      <c r="O3" s="3">
         <v>2020</v>
       </c>
-      <c r="P3" s="118">
+      <c r="P3" s="3">
         <v>2020</v>
       </c>
-      <c r="Q3" s="118">
+      <c r="Q3" s="3">
         <v>2020</v>
       </c>
-      <c r="R3" s="118">
+      <c r="R3" s="3">
         <v>2020</v>
       </c>
-      <c r="S3" s="118">
+      <c r="S3" s="3">
         <v>2020</v>
       </c>
-      <c r="T3" s="118">
+      <c r="T3" s="3">
         <v>2020</v>
       </c>
-      <c r="U3" s="118">
+      <c r="U3" s="3">
         <v>2020</v>
       </c>
-      <c r="V3" s="118">
+      <c r="V3" s="3">
         <v>2020</v>
       </c>
-      <c r="W3" s="118">
+      <c r="W3" s="3">
         <v>2020</v>
       </c>
-      <c r="X3" s="118">
+      <c r="X3" s="3">
         <v>2020</v>
       </c>
-      <c r="Y3" s="118">
+      <c r="Y3" s="3">
         <v>2020</v>
       </c>
-      <c r="Z3" s="118">
+      <c r="Z3" s="3">
         <v>2020</v>
       </c>
     </row>
     <row r="4" spans="1:26" s="6" customFormat="1" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="133"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="117"/>
       <c r="E4" s="34"/>
       <c r="F4" s="15" t="str">
         <f>F2&amp;F3</f>
@@ -2158,7 +1660,7 @@
         <f t="shared" ref="I4:N4" si="1">I2&amp;I3</f>
         <v>Yearly demand (output)All</v>
       </c>
-      <c r="J4" s="111" t="str">
+      <c r="J4" s="101" t="str">
         <f t="shared" si="1"/>
         <v>Produced fromAll</v>
       </c>
@@ -2203,7 +1705,7 @@
         <v>Electrical consumption (kWh/output)2020</v>
       </c>
       <c r="U4" s="15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="V4" s="15" t="str">
         <f t="shared" ref="V4:Z4" si="3">V2&amp;V3</f>
@@ -2227,10 +1729,10 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="8" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="133"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="49" t="s">
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="48" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="8">
@@ -2249,7 +1751,7 @@
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="J5" s="112">
+      <c r="J5" s="102">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -2317,181 +1819,181 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="69" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:26" s="62" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="66" t="s">
-        <v>125</v>
+      <c r="D6" s="59" t="s">
+        <v>122</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" ref="E6:E36" si="7">ROW(D6)-ROW($E$5)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="67">
-        <v>1</v>
-      </c>
-      <c r="G6" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="H6" s="67" t="s">
-        <v>151</v>
-      </c>
-      <c r="I6" s="69">
+      <c r="F6" s="60">
+        <v>1</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="I6" s="62">
         <f>430*10^6</f>
         <v>430000000</v>
       </c>
-      <c r="J6" s="68" t="str">
+      <c r="J6" s="61" t="str">
         <f>B11</f>
         <v>Reactant3</v>
       </c>
-      <c r="K6" s="69">
-        <v>0</v>
-      </c>
-      <c r="L6" s="69">
-        <v>1</v>
-      </c>
-      <c r="M6" s="69">
-        <v>0</v>
-      </c>
-      <c r="N6" s="69">
+      <c r="K6" s="62">
+        <v>0</v>
+      </c>
+      <c r="L6" s="62">
+        <v>1</v>
+      </c>
+      <c r="M6" s="62">
+        <v>0</v>
+      </c>
+      <c r="N6" s="62">
         <v>20000</v>
       </c>
-      <c r="O6" s="105">
+      <c r="O6" s="98">
         <v>5.2910052910052912</v>
       </c>
-      <c r="P6" s="69">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="70">
+      <c r="P6" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="63">
         <v>0.4</v>
       </c>
-      <c r="R6" s="70">
+      <c r="R6" s="63">
         <v>0.2</v>
       </c>
-      <c r="S6" s="123">
+      <c r="S6" s="107">
         <v>0.2</v>
       </c>
-      <c r="T6" s="69">
+      <c r="T6" s="62">
         <v>0.38</v>
       </c>
-      <c r="U6" s="69">
+      <c r="U6" s="62">
         <v>4192</v>
       </c>
-      <c r="V6" s="69">
+      <c r="V6" s="62">
         <v>436</v>
       </c>
-      <c r="W6" s="69">
-        <v>0</v>
-      </c>
-      <c r="X6" s="69">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="77">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="69">
+      <c r="W6" s="62">
+        <v>0</v>
+      </c>
+      <c r="X6" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="70">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="62">
         <v>9.3678779051968114E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="69" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="120"/>
-      <c r="B7" s="64" t="s">
+    <row r="7" spans="1:26" s="62" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="116"/>
+      <c r="B7" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="58" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="66" t="s">
-        <v>126</v>
+      <c r="D7" s="59" t="s">
+        <v>123</v>
       </c>
       <c r="E7" s="9">
         <f>ROW(D7)-ROW($E$5)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="67">
-        <v>1</v>
-      </c>
-      <c r="G7" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="H7" s="67" t="s">
-        <v>151</v>
-      </c>
-      <c r="I7" s="69">
+      <c r="F7" s="60">
+        <v>1</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="I7" s="62">
         <f>430*10^6</f>
         <v>430000000</v>
       </c>
-      <c r="J7" s="68" t="str">
+      <c r="J7" s="61" t="str">
         <f>B11</f>
         <v>Reactant3</v>
       </c>
-      <c r="K7" s="69">
-        <v>0</v>
-      </c>
-      <c r="L7" s="69">
-        <v>1</v>
-      </c>
-      <c r="M7" s="69">
-        <v>0</v>
-      </c>
-      <c r="N7" s="69">
+      <c r="K7" s="62">
+        <v>0</v>
+      </c>
+      <c r="L7" s="62">
+        <v>1</v>
+      </c>
+      <c r="M7" s="62">
+        <v>0</v>
+      </c>
+      <c r="N7" s="62">
         <f>N6</f>
         <v>20000</v>
       </c>
-      <c r="O7" s="105">
+      <c r="O7" s="98">
         <v>5.2910052910052912</v>
       </c>
-      <c r="P7" s="69">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="70">
+      <c r="P7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="63">
         <v>0.4</v>
       </c>
-      <c r="R7" s="70">
+      <c r="R7" s="63">
         <v>0.2</v>
       </c>
-      <c r="S7" s="123">
+      <c r="S7" s="107">
         <v>0.2</v>
       </c>
-      <c r="T7" s="69">
+      <c r="T7" s="62">
         <v>0.83</v>
       </c>
-      <c r="U7" s="69">
+      <c r="U7" s="62">
         <v>4192</v>
       </c>
-      <c r="V7" s="69">
+      <c r="V7" s="62">
         <v>828</v>
       </c>
-      <c r="W7" s="69">
-        <v>0</v>
-      </c>
-      <c r="X7" s="69">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="77">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="69">
+      <c r="W7" s="62">
+        <v>0</v>
+      </c>
+      <c r="X7" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="70">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="62">
         <v>9.3678779051968114E-2</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A8" s="120"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="19" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>121</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="7"/>
@@ -2501,15 +2003,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="113" t="s">
+      <c r="J8" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K8">
@@ -2536,7 +2038,7 @@
       <c r="R8" s="13">
         <v>1</v>
       </c>
-      <c r="S8" s="124">
+      <c r="S8" s="108">
         <v>1</v>
       </c>
       <c r="T8">
@@ -2561,223 +2063,223 @@
         <v>0.10185220882315059</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="82" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="120"/>
-      <c r="B9" s="78" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="79" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="80" t="s">
-        <v>112</v>
+    <row r="9" spans="1:26" s="75" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="116"/>
+      <c r="B9" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>110</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="F9" s="81">
-        <v>1</v>
-      </c>
-      <c r="G9" s="81" t="s">
+      <c r="F9" s="74">
+        <v>1</v>
+      </c>
+      <c r="G9" s="74" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="H9" s="81" t="s">
-        <v>147</v>
-      </c>
-      <c r="I9" s="82">
-        <v>0</v>
-      </c>
-      <c r="J9" s="83" t="str">
+      <c r="I9" s="75">
+        <v>0</v>
+      </c>
+      <c r="J9" s="76" t="str">
         <f>B8</f>
         <v>Reactant1</v>
       </c>
-      <c r="K9" s="82">
-        <v>0</v>
-      </c>
-      <c r="L9" s="82">
-        <v>1</v>
-      </c>
-      <c r="M9" s="82">
-        <v>1</v>
-      </c>
-      <c r="N9" s="82">
+      <c r="K9" s="75">
+        <v>0</v>
+      </c>
+      <c r="L9" s="75">
+        <v>1</v>
+      </c>
+      <c r="M9" s="75">
+        <v>1</v>
+      </c>
+      <c r="N9" s="75">
         <v>20000</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="75">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P9" s="82">
+      <c r="P9" s="75">
         <v>7.07</v>
       </c>
-      <c r="Q9" s="84">
-        <v>0</v>
-      </c>
-      <c r="R9" s="84">
-        <v>1</v>
-      </c>
-      <c r="S9" s="125">
-        <v>1</v>
-      </c>
-      <c r="T9" s="82">
+      <c r="Q9" s="77">
+        <v>0</v>
+      </c>
+      <c r="R9" s="77">
+        <v>1</v>
+      </c>
+      <c r="S9" s="109">
+        <v>1</v>
+      </c>
+      <c r="T9" s="75">
         <v>51.5</v>
       </c>
-      <c r="U9" s="82">
+      <c r="U9" s="75">
         <v>56467</v>
       </c>
-      <c r="V9" s="82">
+      <c r="V9" s="75">
         <v>1129</v>
       </c>
-      <c r="W9" s="82">
-        <v>0</v>
-      </c>
-      <c r="X9" s="82">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="82">
+      <c r="W9" s="75">
+        <v>0</v>
+      </c>
+      <c r="X9" s="75">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="78">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="75">
         <v>9.3678779051968114E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="90" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="120"/>
-      <c r="B10" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="87" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="88" t="s">
+    <row r="10" spans="1:26" s="83" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="116"/>
+      <c r="B10" s="79" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="80" t="s">
         <v>115</v>
+      </c>
+      <c r="D10" s="81" t="s">
+        <v>112</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="F10" s="89">
-        <v>1</v>
-      </c>
-      <c r="G10" s="89" t="s">
+      <c r="F10" s="82">
+        <v>1</v>
+      </c>
+      <c r="G10" s="82" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="H10" s="89" t="s">
-        <v>147</v>
-      </c>
-      <c r="I10" s="90">
-        <v>0</v>
-      </c>
-      <c r="J10" s="91" t="str">
+      <c r="I10" s="83">
+        <v>0</v>
+      </c>
+      <c r="J10" s="84" t="str">
         <f>B8</f>
         <v>Reactant1</v>
       </c>
-      <c r="K10" s="90">
-        <v>0</v>
-      </c>
-      <c r="L10" s="90">
-        <v>1</v>
-      </c>
-      <c r="M10" s="90">
-        <v>1</v>
-      </c>
-      <c r="N10" s="90">
+      <c r="K10" s="83">
+        <v>0</v>
+      </c>
+      <c r="L10" s="83">
+        <v>1</v>
+      </c>
+      <c r="M10" s="83">
+        <v>1</v>
+      </c>
+      <c r="N10" s="83">
         <f>N9</f>
         <v>20000</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="83">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="P10" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="92">
-        <v>0</v>
-      </c>
-      <c r="R10" s="92">
-        <v>1</v>
-      </c>
-      <c r="S10" s="126">
-        <v>1</v>
-      </c>
-      <c r="T10" s="93">
+      <c r="P10" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="85">
+        <v>0</v>
+      </c>
+      <c r="R10" s="85">
+        <v>1</v>
+      </c>
+      <c r="S10" s="110">
+        <v>1</v>
+      </c>
+      <c r="T10" s="86">
         <v>37.9</v>
       </c>
-      <c r="U10" s="93">
+      <c r="U10" s="86">
         <v>131493</v>
       </c>
-      <c r="V10" s="90">
+      <c r="V10" s="83">
         <v>3945</v>
       </c>
-      <c r="W10" s="90">
-        <v>0</v>
-      </c>
-      <c r="X10" s="90">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="94">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="90">
+      <c r="W10" s="83">
+        <v>0</v>
+      </c>
+      <c r="X10" s="83">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="87">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="83">
         <v>9.3678779051968114E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="57" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="120"/>
-      <c r="B11" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="55" t="s">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A11" s="116"/>
+      <c r="B11" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="F11" s="108">
-        <v>1</v>
-      </c>
-      <c r="G11" s="108" t="s">
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H11" s="108" t="s">
-        <v>147</v>
-      </c>
       <c r="I11" s="43">
         <v>0</v>
       </c>
-      <c r="J11" s="114" t="s">
+      <c r="J11" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="57">
-        <v>0</v>
-      </c>
-      <c r="L11" s="57">
-        <v>0</v>
-      </c>
-      <c r="M11" s="57">
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>-1</v>
       </c>
-      <c r="N11" s="57">
+      <c r="N11">
         <f>N9</f>
         <v>20000</v>
       </c>
       <c r="O11" s="43">
         <v>0</v>
       </c>
-      <c r="P11" s="57">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="109">
-        <v>0</v>
-      </c>
-      <c r="R11" s="109">
-        <v>1</v>
-      </c>
-      <c r="S11" s="109">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="99">
+        <v>0</v>
+      </c>
+      <c r="R11" s="99">
+        <v>1</v>
+      </c>
+      <c r="S11" s="99">
         <v>1</v>
       </c>
       <c r="T11" s="43">
@@ -2798,38 +2300,38 @@
       <c r="Y11" s="43">
         <v>0</v>
       </c>
-      <c r="Z11" s="57">
+      <c r="Z11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:26" s="42" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="120"/>
-      <c r="B12" s="71" t="s">
+      <c r="A12" s="116"/>
+      <c r="B12" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="119" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="73" t="s">
+      <c r="C12" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="66" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="9">
         <f>ROW(D12)-ROW($E$5)</f>
         <v>7</v>
       </c>
-      <c r="F12" s="74">
-        <v>1</v>
-      </c>
-      <c r="G12" s="74" t="s">
-        <v>145</v>
-      </c>
-      <c r="H12" s="74" t="s">
-        <v>153</v>
+      <c r="F12" s="67">
+        <v>1</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>142</v>
+      </c>
+      <c r="H12" s="67" t="s">
+        <v>150</v>
       </c>
       <c r="I12" s="42">
         <v>0</v>
       </c>
-      <c r="J12" s="75" t="str">
+      <c r="J12" s="68" t="str">
         <f>B9</f>
         <v>Product/Reactant2</v>
       </c>
@@ -2852,13 +2354,13 @@
       <c r="P12" s="42">
         <v>0</v>
       </c>
-      <c r="Q12" s="76">
-        <v>0</v>
-      </c>
-      <c r="R12" s="76">
-        <v>1</v>
-      </c>
-      <c r="S12" s="127">
+      <c r="Q12" s="69">
+        <v>0</v>
+      </c>
+      <c r="R12" s="69">
+        <v>1</v>
+      </c>
+      <c r="S12" s="111">
         <v>1</v>
       </c>
       <c r="T12" s="42">
@@ -2884,33 +2386,33 @@
       </c>
     </row>
     <row r="13" spans="1:26" s="42" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="120"/>
-      <c r="B13" s="71" t="s">
+      <c r="A13" s="116"/>
+      <c r="B13" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="72" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="73" t="s">
+      <c r="C13" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="66" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="9">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="F13" s="74">
-        <v>1</v>
-      </c>
-      <c r="G13" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="H13" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="I13" s="95">
-        <v>0</v>
-      </c>
-      <c r="J13" s="75" t="s">
+      <c r="F13" s="67">
+        <v>1</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="H13" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="88">
+        <v>0</v>
+      </c>
+      <c r="J13" s="68" t="s">
         <v>12</v>
       </c>
       <c r="K13" s="42">
@@ -2926,37 +2428,37 @@
         <f>N18</f>
         <v>2000000</v>
       </c>
-      <c r="O13" s="95">
+      <c r="O13" s="88">
         <v>0</v>
       </c>
       <c r="P13" s="42">
         <v>0</v>
       </c>
-      <c r="Q13" s="76">
-        <v>0</v>
-      </c>
-      <c r="R13" s="76">
-        <v>1</v>
-      </c>
-      <c r="S13" s="76">
-        <v>1</v>
-      </c>
-      <c r="T13" s="95">
-        <v>0</v>
-      </c>
-      <c r="U13" s="95">
-        <v>0</v>
-      </c>
-      <c r="V13" s="95">
-        <v>0</v>
-      </c>
-      <c r="W13" s="95">
-        <v>0</v>
-      </c>
-      <c r="X13" s="95">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="95">
+      <c r="Q13" s="69">
+        <v>0</v>
+      </c>
+      <c r="R13" s="69">
+        <v>1</v>
+      </c>
+      <c r="S13" s="69">
+        <v>1</v>
+      </c>
+      <c r="T13" s="88">
+        <v>0</v>
+      </c>
+      <c r="U13" s="88">
+        <v>0</v>
+      </c>
+      <c r="V13" s="88">
+        <v>0</v>
+      </c>
+      <c r="W13" s="88">
+        <v>0</v>
+      </c>
+      <c r="X13" s="88">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="88">
         <v>0</v>
       </c>
       <c r="Z13" s="42">
@@ -2964,331 +2466,331 @@
       </c>
     </row>
     <row r="14" spans="1:26" s="42" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="120"/>
-      <c r="B14" s="71" t="s">
+      <c r="A14" s="116"/>
+      <c r="B14" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="119" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="73" t="s">
+      <c r="C14" s="106" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="66" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="9">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="F14" s="74">
-        <v>1</v>
-      </c>
-      <c r="G14" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="I14" s="95">
-        <v>0</v>
-      </c>
-      <c r="J14" s="75" t="s">
+      <c r="F14" s="67">
+        <v>1</v>
+      </c>
+      <c r="G14" s="67" t="s">
+        <v>143</v>
+      </c>
+      <c r="H14" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="88">
+        <v>0</v>
+      </c>
+      <c r="J14" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="95">
+      <c r="K14" s="88">
         <v>0</v>
       </c>
       <c r="L14" s="42">
         <v>-1</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="88">
         <v>0</v>
       </c>
       <c r="N14" s="42">
         <f>N18</f>
         <v>2000000</v>
       </c>
-      <c r="O14" s="95">
+      <c r="O14" s="88">
         <v>0</v>
       </c>
       <c r="P14" s="42">
         <v>1</v>
       </c>
-      <c r="Q14" s="76">
-        <v>0</v>
-      </c>
-      <c r="R14" s="76">
-        <v>1</v>
-      </c>
-      <c r="S14" s="76">
-        <v>1</v>
-      </c>
-      <c r="T14" s="95">
-        <v>0</v>
-      </c>
-      <c r="U14" s="95">
-        <v>0</v>
-      </c>
-      <c r="V14" s="95">
-        <v>0</v>
-      </c>
-      <c r="W14" s="96">
-        <v>0</v>
-      </c>
-      <c r="X14" s="95">
+      <c r="Q14" s="69">
+        <v>0</v>
+      </c>
+      <c r="R14" s="69">
+        <v>1</v>
+      </c>
+      <c r="S14" s="69">
+        <v>1</v>
+      </c>
+      <c r="T14" s="88">
+        <v>0</v>
+      </c>
+      <c r="U14" s="88">
+        <v>0</v>
+      </c>
+      <c r="V14" s="88">
+        <v>0</v>
+      </c>
+      <c r="W14" s="89">
+        <v>0</v>
+      </c>
+      <c r="X14" s="88">
         <v>2.3E-2</v>
       </c>
-      <c r="Y14" s="95">
+      <c r="Y14" s="88">
         <v>0</v>
       </c>
       <c r="Z14" s="42">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="120"/>
-      <c r="B15" s="58" t="s">
+    <row r="15" spans="1:26" s="54" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="116"/>
+      <c r="B15" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="98" t="s">
-        <v>122</v>
+      <c r="C15" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="91" t="s">
+        <v>119</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="F15" s="60">
-        <v>1</v>
-      </c>
-      <c r="G15" s="60" t="s">
+      <c r="F15" s="53">
+        <v>1</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="H15" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="61">
-        <v>0</v>
-      </c>
-      <c r="J15" s="115" t="s">
+      <c r="I15" s="54">
+        <v>0</v>
+      </c>
+      <c r="J15" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="61">
-        <v>0</v>
-      </c>
-      <c r="L15" s="61">
-        <v>0</v>
-      </c>
-      <c r="M15" s="61">
+      <c r="K15" s="54">
+        <v>0</v>
+      </c>
+      <c r="L15" s="54">
+        <v>0</v>
+      </c>
+      <c r="M15" s="54">
         <v>-1</v>
       </c>
-      <c r="N15" s="61">
+      <c r="N15" s="54">
         <v>20000</v>
       </c>
-      <c r="O15" s="63">
-        <v>0</v>
-      </c>
-      <c r="P15" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="62">
-        <v>0</v>
-      </c>
-      <c r="R15" s="62">
-        <v>1</v>
-      </c>
-      <c r="S15" s="128">
-        <v>1</v>
-      </c>
-      <c r="T15" s="61">
+      <c r="O15" s="56">
+        <v>0</v>
+      </c>
+      <c r="P15" s="54">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="55">
+        <v>0</v>
+      </c>
+      <c r="R15" s="55">
+        <v>1</v>
+      </c>
+      <c r="S15" s="112">
+        <v>1</v>
+      </c>
+      <c r="T15" s="54">
         <v>0.94</v>
       </c>
-      <c r="U15" s="61">
-        <v>0</v>
-      </c>
-      <c r="V15" s="61">
-        <v>0</v>
-      </c>
-      <c r="W15" s="61">
-        <v>0</v>
-      </c>
-      <c r="X15" s="61">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="61">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="61">
+      <c r="U15" s="54">
+        <v>0</v>
+      </c>
+      <c r="V15" s="54">
+        <v>0</v>
+      </c>
+      <c r="W15" s="54">
+        <v>0</v>
+      </c>
+      <c r="X15" s="54">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="54">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="54">
         <v>9.3678779051968114E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="61" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="120"/>
-      <c r="B16" s="58" t="s">
+    <row r="16" spans="1:26" s="54" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="116"/>
+      <c r="B16" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="98" t="s">
-        <v>123</v>
+      <c r="C16" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="91" t="s">
+        <v>120</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="F16" s="60">
-        <v>1</v>
-      </c>
-      <c r="G16" s="60" t="s">
+      <c r="F16" s="53">
+        <v>1</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="H16" s="60" t="s">
-        <v>147</v>
-      </c>
-      <c r="I16" s="61">
-        <v>0</v>
-      </c>
-      <c r="J16" s="115" t="s">
+      <c r="I16" s="54">
+        <v>0</v>
+      </c>
+      <c r="J16" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="61">
-        <v>0</v>
-      </c>
-      <c r="L16" s="61">
-        <v>0</v>
-      </c>
-      <c r="M16" s="61">
-        <v>1</v>
-      </c>
-      <c r="N16" s="61">
+      <c r="K16" s="54">
+        <v>0</v>
+      </c>
+      <c r="L16" s="54">
+        <v>0</v>
+      </c>
+      <c r="M16" s="54">
+        <v>1</v>
+      </c>
+      <c r="N16" s="54">
         <v>20000</v>
       </c>
-      <c r="O16" s="63">
-        <v>0</v>
-      </c>
-      <c r="P16" s="61">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="62">
-        <v>0</v>
-      </c>
-      <c r="R16" s="62">
-        <v>1</v>
-      </c>
-      <c r="S16" s="128">
-        <v>1</v>
-      </c>
-      <c r="T16" s="61">
-        <v>0</v>
-      </c>
-      <c r="U16" s="61">
-        <v>0</v>
-      </c>
-      <c r="V16" s="61">
-        <v>0</v>
-      </c>
-      <c r="W16" s="61">
-        <v>0</v>
-      </c>
-      <c r="X16" s="61">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="61">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" s="103" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="120"/>
-      <c r="B17" s="99" t="s">
+      <c r="O16" s="56">
+        <v>0</v>
+      </c>
+      <c r="P16" s="54">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="55">
+        <v>0</v>
+      </c>
+      <c r="R16" s="55">
+        <v>1</v>
+      </c>
+      <c r="S16" s="112">
+        <v>1</v>
+      </c>
+      <c r="T16" s="54">
+        <v>0</v>
+      </c>
+      <c r="U16" s="54">
+        <v>0</v>
+      </c>
+      <c r="V16" s="54">
+        <v>0</v>
+      </c>
+      <c r="W16" s="54">
+        <v>0</v>
+      </c>
+      <c r="X16" s="54">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="54">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" s="96" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="116"/>
+      <c r="B17" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="100" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="101" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" s="97">
+      <c r="C17" s="93" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="90">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="F17" s="102">
-        <v>1</v>
-      </c>
-      <c r="G17" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="H17" s="102" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="103">
-        <v>0</v>
-      </c>
-      <c r="J17" s="116" t="s">
+      <c r="F17" s="95">
+        <v>1</v>
+      </c>
+      <c r="G17" s="95" t="s">
+        <v>144</v>
+      </c>
+      <c r="H17" s="95" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="96">
+        <v>0</v>
+      </c>
+      <c r="J17" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="103">
-        <v>0</v>
-      </c>
-      <c r="L17" s="103">
-        <v>0</v>
-      </c>
-      <c r="M17" s="103">
-        <v>0</v>
-      </c>
-      <c r="N17" s="103">
+      <c r="K17" s="96">
+        <v>0</v>
+      </c>
+      <c r="L17" s="96">
+        <v>0</v>
+      </c>
+      <c r="M17" s="96">
+        <v>0</v>
+      </c>
+      <c r="N17" s="96">
         <v>20000000</v>
       </c>
-      <c r="O17" s="103">
-        <v>0</v>
-      </c>
-      <c r="P17" s="103">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="104">
+      <c r="O17" s="96">
+        <v>0</v>
+      </c>
+      <c r="P17" s="96">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="97">
         <v>0.09</v>
       </c>
-      <c r="R17" s="104">
-        <v>1</v>
-      </c>
-      <c r="S17" s="129">
-        <v>1</v>
-      </c>
-      <c r="T17" s="103">
-        <v>0</v>
-      </c>
-      <c r="U17" s="103">
+      <c r="R17" s="97">
+        <v>1</v>
+      </c>
+      <c r="S17" s="113">
+        <v>1</v>
+      </c>
+      <c r="T17" s="96">
+        <v>0</v>
+      </c>
+      <c r="U17" s="96">
         <v>460.75542459148141</v>
       </c>
-      <c r="V17" s="103">
+      <c r="V17" s="96">
         <v>0.99167600700525393</v>
       </c>
-      <c r="W17" s="103">
-        <v>0</v>
-      </c>
-      <c r="X17" s="103">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="103">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="103">
+      <c r="W17" s="96">
+        <v>0</v>
+      </c>
+      <c r="X17" s="96">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="96">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="96">
         <v>8.174285816161557E-2</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="132" t="s">
+      <c r="A18" s="116" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>32</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -3301,15 +2803,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18" s="113" t="s">
+      <c r="J18" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K18">
@@ -3336,7 +2838,7 @@
       <c r="R18" s="13">
         <v>1</v>
       </c>
-      <c r="S18" s="124">
+      <c r="S18" s="108">
         <v>1</v>
       </c>
       <c r="T18">
@@ -3362,12 +2864,12 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="132"/>
+      <c r="A19" s="116"/>
       <c r="B19" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>30</v>
@@ -3380,15 +2882,15 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="113" t="s">
+      <c r="J19" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K19">
@@ -3416,7 +2918,7 @@
       <c r="R19" s="13">
         <v>1</v>
       </c>
-      <c r="S19" s="124">
+      <c r="S19" s="108">
         <v>1</v>
       </c>
       <c r="T19">
@@ -3442,13 +2944,13 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A20" s="132"/>
+      <c r="A20" s="116"/>
       <c r="B20" s="12" t="str">
         <f>CONCATENATE("RPU_"&amp;D20)</f>
         <v>RPU_ON_SP198-HH100</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>90</v>
@@ -3461,15 +2963,15 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
-      <c r="J20" s="113" t="s">
+      <c r="J20" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K20">
@@ -3497,7 +2999,7 @@
       <c r="R20" s="13">
         <v>1</v>
       </c>
-      <c r="S20" s="124">
+      <c r="S20" s="108">
         <v>1</v>
       </c>
       <c r="T20">
@@ -3523,13 +3025,13 @@
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A21" s="132"/>
+      <c r="A21" s="116"/>
       <c r="B21" s="12" t="str">
         <f t="shared" ref="B21:B31" si="9">CONCATENATE("RPU_"&amp;D21)</f>
         <v>RPU_ON_SP198-HH150</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>33</v>
@@ -3542,15 +3044,15 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-      <c r="J21" s="113" t="s">
+      <c r="J21" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K21">
@@ -3578,7 +3080,7 @@
       <c r="R21" s="13">
         <v>1</v>
       </c>
-      <c r="S21" s="124">
+      <c r="S21" s="108">
         <v>1</v>
       </c>
       <c r="T21">
@@ -3604,13 +3106,13 @@
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A22" s="132"/>
+      <c r="A22" s="116"/>
       <c r="B22" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP237-HH100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>34</v>
@@ -3623,15 +3125,15 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
-      <c r="J22" s="113" t="s">
+      <c r="J22" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K22">
@@ -3659,7 +3161,7 @@
       <c r="R22" s="13">
         <v>1</v>
       </c>
-      <c r="S22" s="124">
+      <c r="S22" s="108">
         <v>1</v>
       </c>
       <c r="T22">
@@ -3685,13 +3187,13 @@
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A23" s="132"/>
+      <c r="A23" s="116"/>
       <c r="B23" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP237-HH150</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
@@ -3704,15 +3206,15 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
-      <c r="J23" s="113" t="s">
+      <c r="J23" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K23">
@@ -3740,7 +3242,7 @@
       <c r="R23" s="13">
         <v>1</v>
       </c>
-      <c r="S23" s="124">
+      <c r="S23" s="108">
         <v>1</v>
       </c>
       <c r="T23">
@@ -3766,13 +3268,13 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A24" s="132"/>
+      <c r="A24" s="116"/>
       <c r="B24" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP277-HH100</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>36</v>
@@ -3785,15 +3287,15 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24" s="113" t="s">
+      <c r="J24" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K24">
@@ -3821,7 +3323,7 @@
       <c r="R24" s="13">
         <v>1</v>
       </c>
-      <c r="S24" s="124">
+      <c r="S24" s="108">
         <v>1</v>
       </c>
       <c r="T24">
@@ -3847,13 +3349,13 @@
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A25" s="132"/>
+      <c r="A25" s="116"/>
       <c r="B25" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP277-HH150</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>37</v>
@@ -3866,15 +3368,15 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
-      <c r="J25" s="113" t="s">
+      <c r="J25" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K25">
@@ -3902,7 +3404,7 @@
       <c r="R25" s="13">
         <v>1</v>
       </c>
-      <c r="S25" s="124">
+      <c r="S25" s="108">
         <v>1</v>
       </c>
       <c r="T25">
@@ -3928,13 +3430,13 @@
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A26" s="132"/>
+      <c r="A26" s="116"/>
       <c r="B26" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP321-HH100</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>38</v>
@@ -3947,15 +3449,15 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
-      <c r="J26" s="113" t="s">
+      <c r="J26" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K26">
@@ -3983,7 +3485,7 @@
       <c r="R26" s="13">
         <v>1</v>
       </c>
-      <c r="S26" s="124">
+      <c r="S26" s="108">
         <v>1</v>
       </c>
       <c r="T26">
@@ -4009,13 +3511,13 @@
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A27" s="132"/>
+      <c r="A27" s="116"/>
       <c r="B27" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_ON_SP321-HH150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>39</v>
@@ -4028,15 +3530,15 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="113" t="s">
+      <c r="J27" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K27">
@@ -4064,7 +3566,7 @@
       <c r="R27" s="13">
         <v>1</v>
       </c>
-      <c r="S27" s="124">
+      <c r="S27" s="108">
         <v>1</v>
       </c>
       <c r="T27">
@@ -4090,13 +3592,13 @@
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A28" s="132"/>
+      <c r="A28" s="116"/>
       <c r="B28" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_OFF_SP379-HH100</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>40</v>
@@ -4109,15 +3611,15 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="J28" s="113" t="s">
+      <c r="J28" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K28">
@@ -4145,7 +3647,7 @@
       <c r="R28" s="13">
         <v>1</v>
       </c>
-      <c r="S28" s="124">
+      <c r="S28" s="108">
         <v>1</v>
       </c>
       <c r="T28">
@@ -4171,13 +3673,13 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A29" s="132"/>
+      <c r="A29" s="116"/>
       <c r="B29" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_OFF_SP379-HH150</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>41</v>
@@ -4190,15 +3692,15 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29" s="113" t="s">
+      <c r="J29" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K29">
@@ -4226,7 +3728,7 @@
       <c r="R29" s="13">
         <v>1</v>
       </c>
-      <c r="S29" s="124">
+      <c r="S29" s="108">
         <v>1</v>
       </c>
       <c r="T29">
@@ -4252,13 +3754,13 @@
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A30" s="132"/>
+      <c r="A30" s="116"/>
       <c r="B30" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_OFF_SP450-HH100</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>42</v>
@@ -4271,15 +3773,15 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" s="113" t="s">
+      <c r="J30" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K30">
@@ -4307,7 +3809,7 @@
       <c r="R30" s="13">
         <v>1</v>
       </c>
-      <c r="S30" s="124">
+      <c r="S30" s="108">
         <v>1</v>
       </c>
       <c r="T30">
@@ -4333,13 +3835,13 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A31" s="132"/>
+      <c r="A31" s="116"/>
       <c r="B31" s="12" t="str">
         <f t="shared" si="9"/>
         <v>RPU_OFF_SP450-HH150</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>91</v>
@@ -4352,15 +3854,15 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="113" t="s">
+      <c r="J31" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K31">
@@ -4388,7 +3890,7 @@
       <c r="R31" s="13">
         <v>1</v>
       </c>
-      <c r="S31" s="124">
+      <c r="S31" s="108">
         <v>1</v>
       </c>
       <c r="T31">
@@ -4414,7 +3916,7 @@
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A32" s="132"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="12" t="s">
         <v>17</v>
       </c>
@@ -4432,15 +3934,15 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" s="113" t="s">
+      <c r="J32" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K32">
@@ -4468,7 +3970,7 @@
       <c r="R32" s="13">
         <v>1</v>
       </c>
-      <c r="S32" s="124">
+      <c r="S32" s="108">
         <v>1</v>
       </c>
       <c r="T32">
@@ -4494,15 +3996,15 @@
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A33" s="132"/>
+      <c r="A33" s="116"/>
       <c r="B33" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E33" s="9">
         <f t="shared" si="7"/>
@@ -4512,15 +4014,15 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" s="113" t="s">
+      <c r="J33" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K33">
@@ -4547,7 +4049,7 @@
       <c r="R33" s="13">
         <v>1</v>
       </c>
-      <c r="S33" s="124">
+      <c r="S33" s="108">
         <v>1</v>
       </c>
       <c r="T33">
@@ -4573,12 +4075,12 @@
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A34" s="132"/>
+      <c r="A34" s="116"/>
       <c r="B34" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>26</v>
@@ -4591,15 +4093,15 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" s="113" t="s">
+      <c r="J34" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K34">
@@ -4627,7 +4129,7 @@
       <c r="R34" s="13">
         <v>1</v>
       </c>
-      <c r="S34" s="124">
+      <c r="S34" s="108">
         <v>1</v>
       </c>
       <c r="T34">
@@ -4653,12 +4155,12 @@
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A35" s="132"/>
+      <c r="A35" s="116"/>
       <c r="B35" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>27</v>
@@ -4671,15 +4173,15 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" s="113" t="s">
+      <c r="J35" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K35">
@@ -4707,7 +4209,7 @@
       <c r="R35" s="13">
         <v>1</v>
       </c>
-      <c r="S35" s="124">
+      <c r="S35" s="108">
         <v>1</v>
       </c>
       <c r="T35">
@@ -4733,12 +4235,12 @@
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.35">
-      <c r="A36" s="132"/>
+      <c r="A36" s="116"/>
       <c r="B36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>28</v>
@@ -4751,15 +4253,15 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" s="113" t="s">
+      <c r="J36" s="103" t="s">
         <v>12</v>
       </c>
       <c r="K36">
@@ -4786,7 +4288,7 @@
       <c r="R36" s="13">
         <v>1</v>
       </c>
-      <c r="S36" s="124">
+      <c r="S36" s="108">
         <v>1</v>
       </c>
       <c r="T36">
@@ -4812,12 +4314,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A36"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C2:C5"/>
+    <mergeCell ref="A6:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293"/>
@@ -4825,7 +4328,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4837,7 +4340,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="56"/>
+      <c r="A1" s="14"/>
       <c r="B1" s="6" t="s">
         <v>92</v>
       </c>
@@ -4849,7 +4352,6 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="57"/>
       <c r="B2" s="6" t="s">
         <v>85</v>
       </c>
@@ -4861,7 +4363,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="56"/>
+      <c r="A3" s="14"/>
       <c r="B3" t="s">
         <v>58</v>
       </c>
@@ -4873,7 +4375,6 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="57"/>
       <c r="B4" t="s">
         <v>69</v>
       </c>
@@ -4943,10 +4444,10 @@
         <f>Data_base_case!D8</f>
         <v>Water supply (desalination plant)</v>
       </c>
-      <c r="C8" s="48">
-        <v>1</v>
-      </c>
-      <c r="D8" s="48">
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5097,10 +4598,10 @@
         <f>Data_base_case!D17</f>
         <v>H2 storage (buried pipes)</v>
       </c>
-      <c r="C17" s="48">
-        <v>1</v>
-      </c>
-      <c r="D17" s="48">
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5113,10 +4614,10 @@
         <f>Data_base_case!D18</f>
         <v>Solar fixed</v>
       </c>
-      <c r="C18" s="48">
-        <v>1</v>
-      </c>
-      <c r="D18" s="48">
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5129,10 +4630,10 @@
         <f>Data_base_case!D19</f>
         <v>Solar tracking</v>
       </c>
-      <c r="C19" s="48">
-        <v>1</v>
-      </c>
-      <c r="D19" s="48">
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5145,10 +4646,10 @@
         <f>Data_base_case!D20</f>
         <v>ON_SP198-HH100</v>
       </c>
-      <c r="C20" s="48">
-        <v>1</v>
-      </c>
-      <c r="D20" s="48">
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5161,10 +4662,10 @@
         <f>Data_base_case!D21</f>
         <v>ON_SP198-HH150</v>
       </c>
-      <c r="C21" s="48">
-        <v>1</v>
-      </c>
-      <c r="D21" s="48">
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5177,10 +4678,10 @@
         <f>Data_base_case!D22</f>
         <v>ON_SP237-HH100</v>
       </c>
-      <c r="C22" s="48">
-        <v>1</v>
-      </c>
-      <c r="D22" s="48">
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5193,10 +4694,10 @@
         <f>Data_base_case!D23</f>
         <v>ON_SP237-HH150</v>
       </c>
-      <c r="C23" s="48">
-        <v>1</v>
-      </c>
-      <c r="D23" s="48">
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5209,10 +4710,10 @@
         <f>Data_base_case!D24</f>
         <v>ON_SP277-HH100</v>
       </c>
-      <c r="C24" s="48">
-        <v>1</v>
-      </c>
-      <c r="D24" s="48">
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5225,10 +4726,10 @@
         <f>Data_base_case!D25</f>
         <v>ON_SP277-HH150</v>
       </c>
-      <c r="C25" s="48">
-        <v>1</v>
-      </c>
-      <c r="D25" s="48">
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5241,10 +4742,10 @@
         <f>Data_base_case!D26</f>
         <v>ON_SP321-HH100</v>
       </c>
-      <c r="C26" s="48">
-        <v>1</v>
-      </c>
-      <c r="D26" s="48">
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5257,10 +4758,10 @@
         <f>Data_base_case!D27</f>
         <v>ON_SP321-HH150</v>
       </c>
-      <c r="C27" s="48">
-        <v>1</v>
-      </c>
-      <c r="D27" s="48">
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5414,10 +4915,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C6:D36">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5427,9 +4928,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:EJ10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.36328125" style="1" customWidth="1"/>
@@ -5446,19 +4947,19 @@
     <col min="16" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:140" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:140" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:140" s="16" customFormat="1" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>79</v>
@@ -5481,519 +4982,11 @@
       <c r="H4" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="16" t="str">
-        <f>Data_base_case!F2&amp;Data_base_case!F3</f>
-        <v>Used (1 or 0)All</v>
-      </c>
-      <c r="O4" s="16" t="str">
-        <f>Data_base_case!G2&amp;Data_base_case!G3</f>
-        <v>Capacity unitsAll</v>
-      </c>
-      <c r="P4" s="16" t="str">
-        <f>Data_base_case!I2&amp;Data_base_case!I3</f>
-        <v>Yearly demand (output)All</v>
-      </c>
-      <c r="Q4" s="16" t="str">
-        <f>Data_base_case!J2&amp;Data_base_case!J3</f>
-        <v>Produced fromAll</v>
-      </c>
-      <c r="R4" s="16" t="str">
-        <f>Data_base_case!K2&amp;Data_base_case!K3</f>
-        <v>El balanceAll</v>
-      </c>
-      <c r="S4" s="16" t="str">
-        <f>Data_base_case!L2&amp;Data_base_case!L3</f>
-        <v>Heat balanceAll</v>
-      </c>
-      <c r="T4" s="16" t="str">
-        <f>Data_base_case!N2&amp;Data_base_case!N3</f>
-        <v>Max CapacityAll</v>
-      </c>
-      <c r="U4" s="16" t="str">
-        <f>Data_base_case!M2&amp;Data_base_case!M3</f>
-        <v>H2 balanceAll</v>
-      </c>
-      <c r="V4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="W4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="X4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Y4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA4" s="16" t="str">
-        <f>Data_base_case!O2&amp;Data_base_case!O3</f>
-        <v>Fuel production rate (kg output/kg input)2020</v>
-      </c>
-      <c r="AB4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AD4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AE4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AF4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AG4" s="16" t="str">
-        <f>Data_base_case!P2&amp;Data_base_case!P3</f>
-        <v>Heat generated (kWh/output)2020</v>
-      </c>
-      <c r="AH4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AI4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AJ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AK4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AL4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AM4" s="16" t="str">
-        <f>Data_base_case!Q2&amp;Data_base_case!Q3</f>
-        <v>Load min (% of max capacity)2020</v>
-      </c>
-      <c r="AN4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AO4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AP4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AQ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AR4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AS4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AT4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AU4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AV4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AW4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AX4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AY4" s="16" t="str">
-        <f>Data_base_case!R2&amp;Data_base_case!R3</f>
-        <v>Ramp up (% of capacity /h)2020</v>
-      </c>
-      <c r="AZ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BA4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BB4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BC4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BD4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BE4" s="16" t="str">
-        <f>Data_base_case!S2&amp;Data_base_case!S3</f>
-        <v>Ramp down (% of capacity /h)2020</v>
-      </c>
-      <c r="BF4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BG4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BH4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BI4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BJ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BK4" s="16" t="str">
-        <f>Data_base_case!T2&amp;Data_base_case!T3</f>
-        <v>Electrical consumption (kWh/output)2020</v>
-      </c>
-      <c r="BL4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BM4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BN4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BO4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BP4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BQ4" s="16" t="str">
-        <f>Data_base_case!U2&amp;Data_base_case!U3</f>
-        <v>Investment (EUR/Capacity installed)2020</v>
-      </c>
-      <c r="BR4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BS4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BT4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BU4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BV4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BW4" s="16" t="str">
-        <f>Data_base_case!V2&amp;Data_base_case!V3</f>
-        <v>Fixed cost (EUR/Capacity installed/y)2020</v>
-      </c>
-      <c r="BX4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BY4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="BZ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CA4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CB4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CC4" s="16" t="str">
-        <f>Data_base_case!W2&amp;Data_base_case!W3</f>
-        <v>Variable cost (EUR/output)2020</v>
-      </c>
-      <c r="CD4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CE4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CF4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CG4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CH4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CI4" s="16" t="str">
-        <f>Data_base_case!X2&amp;Data_base_case!X3</f>
-        <v>Fuel selling price (EUR/output)2020</v>
-      </c>
-      <c r="CJ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CK4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CL4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CM4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CN4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CO4" s="16" t="str">
-        <f>Data_base_case!Y2&amp;Data_base_case!Y3</f>
-        <v>Fuel buying price (EUR/output)2020</v>
-      </c>
-      <c r="CP4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CQ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CR4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CS4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CT4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CU4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CV4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CW4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CX4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CY4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="CZ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DA4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DB4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DC4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DD4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DE4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DF4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DG4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DH4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DI4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DJ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DK4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DL4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DM4" s="16" t="str">
-        <f>Data_base_case!Z2&amp;Data_base_case!Z3</f>
-        <v>Annuity factor2020</v>
-      </c>
-      <c r="DN4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DO4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DP4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DQ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DR4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DS4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DT4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DU4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DV4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DW4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DX4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DY4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="DZ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EA4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EB4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EC4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="ED4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EE4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EF4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EG4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EH4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EI4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="EJ4" s="16" t="e">
-        <f>Data_base_case!#REF!&amp;Data_base_case!#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:140" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:8" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="35"/>
       <c r="B5" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>25</v>
@@ -6016,16 +5009,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:140" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="str">
         <f>B5</f>
         <v>Semi-islanded</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" s="38" t="str">
         <f>Data_base_case!$Q$1</f>
@@ -6045,7 +5038,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="7" spans="1:140" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21"/>
       <c r="B7" s="1" t="s">
         <v>84</v>
@@ -6072,7 +5065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:140" s="30" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" s="30" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>84</v>
       </c>
@@ -6080,7 +5073,7 @@
         <v>94</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D8" s="30" t="str">
         <f>Data_base_case!$Q$1</f>
@@ -6100,13 +5093,13 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:140" s="23" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="23" t="s">
         <v>86</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D9" s="23" t="str">
         <f>Data_base_case!$Q$1</f>
@@ -6126,15 +5119,15 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:140" s="40" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" s="40" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D10" s="40" t="str">
         <f>Data_base_case!$Q$1</f>
@@ -6161,9 +5154,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
@@ -6173,44 +5166,42 @@
     <col min="5" max="5" width="6.1796875" style="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1796875" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.26953125" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" style="14" customWidth="1"/>
-    <col min="10" max="10" width="10.54296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.26953125" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B1" s="135" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B1" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="136"/>
-    </row>
-    <row r="2" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="137" t="s">
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="120"/>
+    </row>
+    <row r="2" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="121" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="122" t="s">
         <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>66</v>
@@ -6221,82 +5212,76 @@
       <c r="G2" s="2">
         <v>2020</v>
       </c>
-      <c r="H2" s="137" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" s="137" t="s">
-        <v>97</v>
+      <c r="H2" s="121" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="L2" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="K2" s="50" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B3" s="137"/>
-      <c r="C3" s="138"/>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
       <c r="D3" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="121"/>
+      <c r="I3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="53"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="50"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B4" s="121"/>
+      <c r="C4" s="122"/>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="B5" s="137"/>
-      <c r="C5" s="138"/>
+      <c r="K4" s="50"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="B5" s="121"/>
+      <c r="C5" s="122"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="52"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="54" t="s">
+      <c r="P5" s="29"/>
+      <c r="Q5" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="K6" s="14"/>
-      <c r="L6" s="37"/>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="J6" s="14"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="29"/>
-    </row>
-    <row r="7" spans="1:20" s="25" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="P6" s="29"/>
+    </row>
+    <row r="7" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>56</v>
       </c>
@@ -6307,7 +5292,7 @@
         <v>87</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>57</v>
@@ -6319,58 +5304,55 @@
         <v>95</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="K7" s="26" t="s">
         <v>61</v>
       </c>
+      <c r="L7" s="25" t="s">
+        <v>62</v>
+      </c>
       <c r="M7" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="P7" s="26" t="s">
         <v>72</v>
       </c>
+      <c r="Q7" s="25" t="s">
+        <v>65</v>
+      </c>
       <c r="R7" s="25" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="T7" s="25" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f>ROW(A8)-ROW($A$7)</f>
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>66</v>
@@ -6378,63 +5360,60 @@
       <c r="F8" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="117">
+      <c r="G8" s="49">
         <v>2020</v>
       </c>
-      <c r="H8" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="14" t="str">
-        <f t="shared" ref="I8:I25" si="0">"2019"</f>
+      <c r="H8" s="14" t="str">
+        <f t="shared" ref="H8:H25" si="0">"2019"</f>
         <v>2019</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="I8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K8" t="s">
-        <v>111</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>132</v>
+      <c r="J8" t="s">
+        <v>109</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
       </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
-      <c r="S8" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T8" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f>ROW(A9)-ROW($A$7)</f>
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>66</v>
@@ -6442,63 +5421,60 @@
       <c r="F9" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="117">
+      <c r="G9" s="49">
         <v>2020</v>
       </c>
-      <c r="H9" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="14" t="str">
+      <c r="H9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K9" t="s">
-        <v>111</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>132</v>
+      <c r="J9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P9" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
       </c>
-      <c r="S9" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f>ROW(A10)-ROW($A$7)</f>
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>66</v>
@@ -6506,63 +5482,60 @@
       <c r="F10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="117">
+      <c r="G10" s="49">
         <v>2020</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="14" t="str">
+      <c r="H10" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="I10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K10" t="s">
-        <v>111</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>132</v>
+      <c r="J10" t="s">
+        <v>109</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
       </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="b">
-        <v>1</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>1</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
-      <c r="S10" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" ref="A11:A16" si="1">ROW(A11)-ROW($A$7)</f>
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>66</v>
@@ -6570,63 +5543,60 @@
       <c r="F11" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="49">
         <v>2020</v>
       </c>
-      <c r="H11" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="14" t="str">
+      <c r="H11" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="I11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K11" t="s">
-        <v>111</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>132</v>
+      <c r="J11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
       </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="b">
-        <v>1</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P11" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
       </c>
-      <c r="S11" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>66</v>
@@ -6634,63 +5604,60 @@
       <c r="F12" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="49">
         <v>2020</v>
       </c>
-      <c r="H12" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I12" s="14" t="str">
+      <c r="H12" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="I12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K12" t="s">
-        <v>111</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>132</v>
+      <c r="J12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
       </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
       </c>
-      <c r="S12" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T12" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>66</v>
@@ -6698,63 +5665,60 @@
       <c r="F13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="117">
+      <c r="G13" s="49">
         <v>2020</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="14" t="str">
+      <c r="H13" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="I13" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K13" t="s">
-        <v>111</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>132</v>
+      <c r="J13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
       </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
       </c>
-      <c r="S13" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>66</v>
@@ -6762,63 +5726,60 @@
       <c r="F14" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="117">
+      <c r="G14" s="49">
         <v>2020</v>
       </c>
-      <c r="H14" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="14" t="str">
+      <c r="H14" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="I14" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K14" t="s">
-        <v>111</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>132</v>
+      <c r="J14" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
       </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P14" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
-      <c r="S14" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T14" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>66</v>
@@ -6826,63 +5787,60 @@
       <c r="F15" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="117">
+      <c r="G15" s="49">
         <v>2020</v>
       </c>
-      <c r="H15" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" s="14" t="str">
+      <c r="H15" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="I15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K15" t="s">
-        <v>111</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>132</v>
+      <c r="J15" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="b">
-        <v>1</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P15" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
       </c>
       <c r="R15" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T15" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>66</v>
@@ -6890,63 +5848,60 @@
       <c r="F16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="117">
+      <c r="G16" s="49">
         <v>2020</v>
       </c>
-      <c r="H16" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="14" t="str">
+      <c r="H16" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="I16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K16" t="s">
-        <v>111</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>132</v>
+      <c r="J16" t="s">
+        <v>109</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
       </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P16" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
       </c>
-      <c r="S16" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T16" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" ref="A17:A25" si="2">ROW(A17)-ROW($A$7)</f>
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>66</v>
@@ -6954,63 +5909,60 @@
       <c r="F17" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="117">
+      <c r="G17" s="49">
         <v>2020</v>
       </c>
-      <c r="H17" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="14" t="str">
+      <c r="H17" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="I17" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K17" t="s">
-        <v>111</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>133</v>
+      <c r="J17" t="s">
+        <v>109</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
       </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="b">
-        <v>1</v>
-      </c>
-      <c r="P17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P17" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
       </c>
       <c r="R17" t="b">
         <v>1</v>
       </c>
-      <c r="S17" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T17" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>66</v>
@@ -7018,63 +5970,60 @@
       <c r="F18" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="117">
+      <c r="G18" s="49">
         <v>2020</v>
       </c>
-      <c r="H18" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I18" s="14" t="str">
+      <c r="H18" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="I18" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K18" t="s">
-        <v>111</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>133</v>
+      <c r="J18" t="s">
+        <v>109</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
       </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
-      </c>
-      <c r="P18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P18" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
       </c>
       <c r="R18" t="b">
         <v>1</v>
       </c>
-      <c r="S18" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T18" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>66</v>
@@ -7082,63 +6031,60 @@
       <c r="F19" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G19" s="117">
+      <c r="G19" s="49">
         <v>2020</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" s="14" t="str">
+      <c r="H19" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="I19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K19" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>133</v>
+      <c r="J19" t="s">
+        <v>109</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
       </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
-      </c>
-      <c r="P19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P19" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
-      <c r="S19" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>66</v>
@@ -7146,63 +6092,60 @@
       <c r="F20" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G20" s="117">
+      <c r="G20" s="49">
         <v>2020</v>
       </c>
-      <c r="H20" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I20" s="14" t="str">
+      <c r="H20" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="I20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K20" t="s">
-        <v>111</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>133</v>
+      <c r="J20" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
       </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P20" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>1</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
-      <c r="S20" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>66</v>
@@ -7210,63 +6153,60 @@
       <c r="F21" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="117">
+      <c r="G21" s="49">
         <v>2020</v>
       </c>
-      <c r="H21" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="14" t="str">
+      <c r="H21" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="I21" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K21" t="s">
-        <v>111</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>133</v>
+      <c r="J21" t="s">
+        <v>109</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
       </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="b">
-        <v>1</v>
-      </c>
-      <c r="P21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P21" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
-      <c r="S21" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T21" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>66</v>
@@ -7274,63 +6214,60 @@
       <c r="F22" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="117">
+      <c r="G22" s="49">
         <v>2020</v>
       </c>
-      <c r="H22" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="14" t="str">
+      <c r="H22" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="I22" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K22" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>133</v>
+      <c r="J22" t="s">
+        <v>109</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
       </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="b">
-        <v>1</v>
-      </c>
-      <c r="P22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P22" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
-      <c r="S22" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T22" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>66</v>
@@ -7338,63 +6275,60 @@
       <c r="F23" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="117">
+      <c r="G23" s="49">
         <v>2020</v>
       </c>
-      <c r="H23" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="14" t="str">
+      <c r="H23" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="I23" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K23" t="s">
-        <v>111</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>133</v>
+      <c r="J23" t="s">
+        <v>109</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
       </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
-      </c>
-      <c r="P23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P23" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
       </c>
       <c r="R23" t="b">
         <v>1</v>
       </c>
-      <c r="S23" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T23" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>66</v>
@@ -7402,63 +6336,60 @@
       <c r="F24" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G24" s="117">
+      <c r="G24" s="49">
         <v>2020</v>
       </c>
-      <c r="H24" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="str">
+      <c r="H24" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="I24" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K24" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>133</v>
+      <c r="J24" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
       </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
-      </c>
-      <c r="P24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P24" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
-      <c r="S24" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T24" s="122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>66</v>
@@ -7466,299 +6397,55 @@
       <c r="F25" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G25" s="117">
+      <c r="G25" s="49">
         <v>2020</v>
       </c>
-      <c r="H25" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="14" t="str">
+      <c r="H25" s="14" t="str">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="J25" s="14" t="s">
+      <c r="I25" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K25" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>133</v>
+      <c r="J25" t="s">
+        <v>109</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="b">
-        <v>1</v>
-      </c>
-      <c r="P25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="17" t="b">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="P25" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>1</v>
       </c>
       <c r="R25" t="b">
         <v>1</v>
       </c>
-      <c r="S25" s="122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T25" s="122" t="b">
+      <c r="S25" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="H2:H4"/>
+  <mergeCells count="4">
+    <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
-  <conditionalFormatting sqref="O8:Q16 M8:M25 R8:T8 S9:T25">
-    <cfRule type="cellIs" dxfId="61" priority="863" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="864" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N8">
-    <cfRule type="cellIs" dxfId="59" priority="723" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="724" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R11:R16">
-    <cfRule type="cellIs" dxfId="57" priority="721" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="722" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N10">
-    <cfRule type="cellIs" dxfId="55" priority="717" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="718" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R10">
-    <cfRule type="cellIs" dxfId="53" priority="715" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="716" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9">
-    <cfRule type="cellIs" dxfId="51" priority="711" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="712" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R9">
-    <cfRule type="cellIs" dxfId="49" priority="709" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="710" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N11">
-    <cfRule type="cellIs" dxfId="47" priority="193" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="194" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N12">
-    <cfRule type="cellIs" dxfId="45" priority="185" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="186" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N13">
-    <cfRule type="cellIs" dxfId="43" priority="177" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="178" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N14">
-    <cfRule type="cellIs" dxfId="41" priority="169" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="170" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N15">
-    <cfRule type="cellIs" dxfId="39" priority="161" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="162" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N16">
-    <cfRule type="cellIs" dxfId="37" priority="153" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="154" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O17:Q19 R17">
-    <cfRule type="cellIs" dxfId="35" priority="53" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="54" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N17">
-    <cfRule type="cellIs" dxfId="33" priority="49" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="50" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19">
-    <cfRule type="cellIs" dxfId="31" priority="45" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="46" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="29" priority="43" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="44" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N18">
-    <cfRule type="cellIs" dxfId="27" priority="39" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="40" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R18">
-    <cfRule type="cellIs" dxfId="25" priority="37" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="38" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O20:Q22 R20">
-    <cfRule type="cellIs" dxfId="23" priority="35" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="36" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N20">
-    <cfRule type="cellIs" dxfId="21" priority="31" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="32" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22">
-    <cfRule type="cellIs" dxfId="19" priority="27" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="28" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R22">
-    <cfRule type="cellIs" dxfId="17" priority="25" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="26" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N21">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="22" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R21">
-    <cfRule type="cellIs" dxfId="13" priority="19" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="20" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O23:Q25 R23">
-    <cfRule type="cellIs" dxfId="11" priority="17" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23">
-    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R25">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N24">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>FALSE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R24">
+  <conditionalFormatting sqref="L8:S25">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>

--- a/data/Ammonia_paper/model_inputs/Data_ammonia_paper.xlsx
+++ b/data/Ammonia_paper/model_inputs/Data_ammonia_paper.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA624466-5CAF-4125-999B-B70E5CDA2366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{DA624466-5CAF-4125-999B-B70E5CDA2366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6D85D9-FC28-4244-9806-BA15EB30CF2C}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-1620" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_base_case" sheetId="79" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="155">
   <si>
     <t>Red: Don't change the name without changing the Julia code</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Solar tracking</t>
   </si>
   <si>
-    <t>RPU_Solar_track</t>
-  </si>
-  <si>
     <t>RPU_Solar_fixed</t>
   </si>
   <si>
@@ -505,6 +502,9 @@
   </si>
   <si>
     <t>Yearly demand (output)</t>
+  </si>
+  <si>
+    <t>RPU_Solar_tracking</t>
   </si>
 </sst>
 </file>
@@ -989,7 +989,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -1033,6 +1033,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sources"/>
       <sheetName val="Fuel production cost"/>
@@ -1103,6 +1106,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1380,7 +1387,7 @@
     <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="36" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.453125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.453125" bestFit="1" customWidth="1"/>
@@ -1404,16 +1411,16 @@
       <c r="D1" s="114"/>
       <c r="E1" s="115"/>
       <c r="F1" s="44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G1" s="44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H1" s="44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I1" s="45" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J1" s="100" t="s">
         <v>2</v>
@@ -1427,44 +1434,44 @@
       <c r="M1" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="46" t="s">
         <v>6</v>
       </c>
       <c r="O1" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="47" t="s">
+      <c r="Q1" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="47" t="s">
+      <c r="R1" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="47" t="s">
+      <c r="S1" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="S1" s="47" t="s">
+      <c r="T1" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="47" t="s">
+      <c r="U1" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="V1" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="W1" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="X1" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y1" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z1" s="46" t="s">
         <v>48</v>
-      </c>
-      <c r="U1" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="V1" s="47" t="s">
-        <v>98</v>
-      </c>
-      <c r="W1" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="X1" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y1" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z1" s="46" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:26" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1572,34 +1579,34 @@
       <c r="C3" s="118"/>
       <c r="D3" s="117"/>
       <c r="E3" s="34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J3" s="101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O3" s="3">
         <v>2020</v>
@@ -1705,7 +1712,7 @@
         <v>Electrical consumption (kWh/output)2020</v>
       </c>
       <c r="U4" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="V4" s="15" t="str">
         <f t="shared" ref="V4:Z4" si="3">V2&amp;V3</f>
@@ -1824,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" ref="E6:E36" si="7">ROW(D6)-ROW($E$5)</f>
@@ -1840,10 +1847,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H6" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I6" s="62">
         <f>430*10^6</f>
@@ -1862,8 +1869,8 @@
       <c r="M6" s="62">
         <v>0</v>
       </c>
-      <c r="N6" s="62">
-        <v>20000</v>
+      <c r="N6" s="60" t="s">
+        <v>67</v>
       </c>
       <c r="O6" s="98">
         <v>5.2910052910052912</v>
@@ -1905,13 +1912,13 @@
     <row r="7" spans="1:26" s="62" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="116"/>
       <c r="B7" s="57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="9">
         <f>ROW(D7)-ROW($E$5)</f>
@@ -1921,10 +1928,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H7" s="60" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I7" s="62">
         <f>430*10^6</f>
@@ -1943,9 +1950,9 @@
       <c r="M7" s="62">
         <v>0</v>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="60" t="str">
         <f>N6</f>
-        <v>20000</v>
+        <v>None</v>
       </c>
       <c r="O7" s="98">
         <v>5.2910052910052912</v>
@@ -1987,13 +1994,13 @@
     <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="116"/>
       <c r="B8" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" si="7"/>
@@ -2003,10 +2010,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2023,8 +2030,8 @@
       <c r="M8">
         <v>0</v>
       </c>
-      <c r="N8">
-        <v>400000</v>
+      <c r="N8" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -2066,13 +2073,13 @@
     <row r="9" spans="1:26" s="75" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="116"/>
       <c r="B9" s="71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" s="73" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9" s="9">
         <f t="shared" si="7"/>
@@ -2082,10 +2089,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H9" s="74" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I9" s="75">
         <v>0</v>
@@ -2103,8 +2110,8 @@
       <c r="M9" s="75">
         <v>1</v>
       </c>
-      <c r="N9" s="75">
-        <v>20000</v>
+      <c r="N9" s="74" t="s">
+        <v>67</v>
       </c>
       <c r="O9" s="75">
         <v>6.7000000000000004E-2</v>
@@ -2146,13 +2153,13 @@
     <row r="10" spans="1:26" s="83" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="116"/>
       <c r="B10" s="79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" s="80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10" s="81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" si="7"/>
@@ -2162,10 +2169,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="82" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H10" s="82" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I10" s="83">
         <v>0</v>
@@ -2183,9 +2190,9 @@
       <c r="M10" s="83">
         <v>1</v>
       </c>
-      <c r="N10" s="83">
+      <c r="N10" s="82" t="str">
         <f>N9</f>
-        <v>20000</v>
+        <v>None</v>
       </c>
       <c r="O10" s="83">
         <v>6.7000000000000004E-2</v>
@@ -2227,10 +2234,10 @@
     <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="116"/>
       <c r="B11" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -2243,10 +2250,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I11" s="43">
         <v>0</v>
@@ -2263,9 +2270,9 @@
       <c r="M11">
         <v>-1</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2" t="str">
         <f>N9</f>
-        <v>20000</v>
+        <v>None</v>
       </c>
       <c r="O11" s="43">
         <v>0</v>
@@ -2307,10 +2314,10 @@
     <row r="12" spans="1:26" s="42" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="116"/>
       <c r="B12" s="64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D12" s="66" t="s">
         <v>24</v>
@@ -2323,10 +2330,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H12" s="67" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I12" s="42">
         <v>0</v>
@@ -2344,9 +2351,8 @@
       <c r="M12" s="42">
         <v>0</v>
       </c>
-      <c r="N12" s="42">
-        <f>9*N9</f>
-        <v>180000</v>
+      <c r="N12" s="67" t="s">
+        <v>67</v>
       </c>
       <c r="O12" s="42">
         <v>7.76</v>
@@ -2391,7 +2397,7 @@
         <v>18</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" s="66" t="s">
         <v>22</v>
@@ -2404,10 +2410,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H13" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I13" s="88">
         <v>0</v>
@@ -2424,9 +2430,8 @@
       <c r="M13" s="42">
         <v>0</v>
       </c>
-      <c r="N13" s="42">
-        <f>N18</f>
-        <v>2000000</v>
+      <c r="N13" s="67" t="s">
+        <v>67</v>
       </c>
       <c r="O13" s="88">
         <v>0</v>
@@ -2471,7 +2476,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D14" s="66" t="s">
         <v>23</v>
@@ -2484,10 +2489,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H14" s="67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I14" s="88">
         <v>0</v>
@@ -2504,9 +2509,8 @@
       <c r="M14" s="88">
         <v>0</v>
       </c>
-      <c r="N14" s="42">
-        <f>N18</f>
-        <v>2000000</v>
+      <c r="N14" s="67" t="s">
+        <v>67</v>
       </c>
       <c r="O14" s="88">
         <v>0</v>
@@ -2551,10 +2555,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="91" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E15" s="9">
         <f t="shared" si="7"/>
@@ -2564,10 +2568,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I15" s="54">
         <v>0</v>
@@ -2584,8 +2588,8 @@
       <c r="M15" s="54">
         <v>-1</v>
       </c>
-      <c r="N15" s="54">
-        <v>20000</v>
+      <c r="N15" s="53" t="s">
+        <v>67</v>
       </c>
       <c r="O15" s="56">
         <v>0</v>
@@ -2630,10 +2634,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" s="91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E16" s="9">
         <f t="shared" si="7"/>
@@ -2643,10 +2647,10 @@
         <v>1</v>
       </c>
       <c r="G16" s="53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H16" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="54">
         <v>0</v>
@@ -2663,8 +2667,8 @@
       <c r="M16" s="54">
         <v>1</v>
       </c>
-      <c r="N16" s="54">
-        <v>20000</v>
+      <c r="N16" s="53" t="s">
+        <v>67</v>
       </c>
       <c r="O16" s="56">
         <v>0</v>
@@ -2709,10 +2713,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="93" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D17" s="94" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="90">
         <f t="shared" si="7"/>
@@ -2722,10 +2726,10 @@
         <v>1</v>
       </c>
       <c r="G17" s="95" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H17" s="95" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I17" s="96">
         <v>0</v>
@@ -2742,8 +2746,8 @@
       <c r="M17" s="96">
         <v>0</v>
       </c>
-      <c r="N17" s="96">
-        <v>20000000</v>
+      <c r="N17" s="95" t="s">
+        <v>67</v>
       </c>
       <c r="O17" s="96">
         <v>0</v>
@@ -2787,10 +2791,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -2803,10 +2807,10 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2823,8 +2827,8 @@
       <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18">
-        <v>2000000</v>
+      <c r="N18" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O18" s="10">
         <v>0</v>
@@ -2866,10 +2870,10 @@
     <row r="19" spans="1:26" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="116"/>
       <c r="B19" s="12" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>30</v>
@@ -2882,10 +2886,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2902,9 +2906,8 @@
       <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19">
-        <f t="shared" ref="N19:N32" si="8">$N$18</f>
-        <v>2000000</v>
+      <c r="N19" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O19" s="10">
         <v>0</v>
@@ -2950,10 +2953,10 @@
         <v>RPU_ON_SP198-HH100</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="9">
         <f t="shared" si="7"/>
@@ -2963,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2983,9 +2986,8 @@
       <c r="M20">
         <v>0</v>
       </c>
-      <c r="N20">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N20" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O20" s="10">
         <v>0</v>
@@ -3027,14 +3029,14 @@
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" s="116"/>
       <c r="B21" s="12" t="str">
-        <f t="shared" ref="B21:B31" si="9">CONCATENATE("RPU_"&amp;D21)</f>
+        <f t="shared" ref="B21:B31" si="8">CONCATENATE("RPU_"&amp;D21)</f>
         <v>RPU_ON_SP198-HH150</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" s="9">
         <f t="shared" si="7"/>
@@ -3044,10 +3046,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3064,9 +3066,8 @@
       <c r="M21">
         <v>0</v>
       </c>
-      <c r="N21">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N21" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O21" s="10">
         <v>0</v>
@@ -3108,14 +3109,14 @@
     <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" s="116"/>
       <c r="B22" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP237-HH100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="9">
         <f t="shared" si="7"/>
@@ -3125,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3145,9 +3146,8 @@
       <c r="M22">
         <v>0</v>
       </c>
-      <c r="N22">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N22" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O22" s="10">
         <v>0</v>
@@ -3189,14 +3189,14 @@
     <row r="23" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A23" s="116"/>
       <c r="B23" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP237-HH150</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23" s="9">
         <f t="shared" si="7"/>
@@ -3206,10 +3206,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3226,9 +3226,8 @@
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="N23">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N23" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O23" s="10">
         <v>0</v>
@@ -3270,14 +3269,14 @@
     <row r="24" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A24" s="116"/>
       <c r="B24" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP277-HH100</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="9">
         <f t="shared" si="7"/>
@@ -3287,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3307,9 +3306,8 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N24" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O24" s="10">
         <v>0</v>
@@ -3351,14 +3349,14 @@
     <row r="25" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A25" s="116"/>
       <c r="B25" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP277-HH150</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="9">
         <f t="shared" si="7"/>
@@ -3368,10 +3366,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3388,9 +3386,8 @@
       <c r="M25">
         <v>0</v>
       </c>
-      <c r="N25">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N25" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -3432,14 +3429,14 @@
     <row r="26" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A26" s="116"/>
       <c r="B26" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP321-HH100</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" s="9">
         <f t="shared" si="7"/>
@@ -3449,10 +3446,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3469,9 +3466,8 @@
       <c r="M26">
         <v>0</v>
       </c>
-      <c r="N26">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N26" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -3513,14 +3509,14 @@
     <row r="27" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A27" s="116"/>
       <c r="B27" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_ON_SP321-HH150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27" s="9">
         <f t="shared" si="7"/>
@@ -3530,10 +3526,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3550,9 +3546,8 @@
       <c r="M27">
         <v>0</v>
       </c>
-      <c r="N27">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N27" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O27" s="10">
         <v>0</v>
@@ -3594,14 +3589,14 @@
     <row r="28" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A28" s="116"/>
       <c r="B28" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_OFF_SP379-HH100</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28" s="9">
         <f t="shared" si="7"/>
@@ -3611,10 +3606,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3631,9 +3626,8 @@
       <c r="M28">
         <v>0</v>
       </c>
-      <c r="N28">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N28" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -3675,14 +3669,14 @@
     <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="116"/>
       <c r="B29" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_OFF_SP379-HH150</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="9">
         <f t="shared" si="7"/>
@@ -3692,10 +3686,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3712,9 +3706,8 @@
       <c r="M29">
         <v>0</v>
       </c>
-      <c r="N29">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N29" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O29" s="10">
         <v>0</v>
@@ -3756,14 +3749,14 @@
     <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" s="116"/>
       <c r="B30" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_OFF_SP450-HH100</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30" s="9">
         <f t="shared" si="7"/>
@@ -3773,10 +3766,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3793,9 +3786,8 @@
       <c r="M30">
         <v>0</v>
       </c>
-      <c r="N30">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N30" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O30" s="10">
         <v>0</v>
@@ -3837,14 +3829,14 @@
     <row r="31" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A31" s="116"/>
       <c r="B31" s="12" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>RPU_OFF_SP450-HH150</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E31" s="9">
         <f t="shared" si="7"/>
@@ -3854,10 +3846,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3874,9 +3866,8 @@
       <c r="M31">
         <v>0</v>
       </c>
-      <c r="N31">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N31" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O31" s="10">
         <v>0</v>
@@ -3934,10 +3925,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3954,9 +3945,8 @@
       <c r="M32">
         <v>0</v>
       </c>
-      <c r="N32">
-        <f t="shared" si="8"/>
-        <v>2000000</v>
+      <c r="N32" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O32" s="10">
         <v>0</v>
@@ -3998,13 +3988,13 @@
     <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="116"/>
       <c r="B33" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="E33" s="9">
         <f t="shared" si="7"/>
@@ -4014,10 +4004,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -4034,8 +4024,8 @@
       <c r="M33">
         <v>0</v>
       </c>
-      <c r="N33">
-        <v>24000</v>
+      <c r="N33" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -4080,7 +4070,7 @@
         <v>13</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>26</v>
@@ -4093,10 +4083,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -4113,9 +4103,8 @@
       <c r="M34">
         <v>0</v>
       </c>
-      <c r="N34">
-        <f>N36/2</f>
-        <v>10000000</v>
+      <c r="N34" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O34" s="10">
         <v>0</v>
@@ -4160,7 +4149,7 @@
         <v>14</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>27</v>
@@ -4173,10 +4162,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4193,9 +4182,8 @@
       <c r="M35">
         <v>0</v>
       </c>
-      <c r="N35">
-        <f>3*N36</f>
-        <v>60000000</v>
+      <c r="N35" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O35" s="10">
         <v>0</v>
@@ -4240,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>28</v>
@@ -4253,10 +4241,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4273,8 +4261,8 @@
       <c r="M36">
         <v>0</v>
       </c>
-      <c r="N36">
-        <v>20000000</v>
+      <c r="N36" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="O36" s="10">
         <v>0</v>
@@ -4342,18 +4330,18 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="14"/>
       <c r="B1" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B2" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="28">
         <v>18.600000000000001</v>
@@ -4365,30 +4353,30 @@
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" ref="C5:D5" si="0">C1&amp;"_"&amp;C3&amp;"_"&amp;C4</f>
@@ -4949,44 +4937,44 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>52</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="16" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="35"/>
       <c r="B5" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>25</v>
@@ -4996,13 +4984,13 @@
         <v>Used (1 or 0)</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="16">
         <v>1</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H5" s="16">
         <f>INDEX(Data_base_case!$D$5:$Z$82,MATCH(Scenarios_definition!C5,Data_base_case!$D$5:$D$82,0),MATCH(Scenarios_definition!D5&amp;Scenarios_definition!G5,Data_base_case!$D$4:$Z$4,0))</f>
@@ -5015,17 +5003,17 @@
         <v>Semi-islanded</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D6" s="38" t="str">
         <f>Data_base_case!$Q$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="38">
         <v>0</v>
@@ -5041,7 +5029,7 @@
     <row r="7" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="21"/>
       <c r="B7" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="str">
         <f>Data_base_case!D32</f>
@@ -5052,13 +5040,13 @@
         <v>Used (1 or 0)</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" s="1">
         <f>INDEX(Data_base_case!$D$5:$Z$82,MATCH(Scenarios_definition!C7,Data_base_case!$D$5:$D$82,0),MATCH(Scenarios_definition!D7&amp;Scenarios_definition!G7,Data_base_case!$D$4:$Z$4,0))</f>
@@ -5067,20 +5055,20 @@
     </row>
     <row r="8" spans="1:8" s="30" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D8" s="30" t="str">
         <f>Data_base_case!$Q$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" s="30">
         <v>1</v>
@@ -5096,17 +5084,17 @@
     <row r="9" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="22"/>
       <c r="B9" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" s="23" t="str">
         <f>Data_base_case!$Q$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9" s="23">
         <v>1</v>
@@ -5121,20 +5109,20 @@
     </row>
     <row r="10" spans="1:8" s="40" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D10" s="40" t="str">
         <f>Data_base_case!$Q$1</f>
         <v>Load min (% of max capacity)</v>
       </c>
       <c r="E10" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10" s="40">
         <v>0</v>
@@ -5181,7 +5169,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B1" s="119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C1" s="119"/>
       <c r="D1" s="119"/>
@@ -5195,47 +5183,47 @@
     </row>
     <row r="2" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="121" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2" s="2">
         <v>2020</v>
       </c>
       <c r="H2" s="121" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3" s="121"/>
       <c r="C3" s="122"/>
       <c r="D3" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="121"/>
       <c r="I3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="50"/>
@@ -5244,7 +5232,7 @@
       <c r="B4" s="121"/>
       <c r="C4" s="122"/>
       <c r="D4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="2"/>
@@ -5269,7 +5257,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="29"/>
       <c r="Q5" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -5283,61 +5271,61 @@
     </row>
     <row r="7" spans="1:19" s="25" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="H7" s="25" t="s">
+      <c r="J7" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="26" t="s">
+      <c r="L7" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="N7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="O7" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="O7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>65</v>
-      </c>
       <c r="R7" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="S7" s="25" t="s">
         <v>152</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
@@ -5346,19 +5334,19 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="49">
         <v>2020</v>
@@ -5368,13 +5356,13 @@
         <v>2019</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -5407,19 +5395,19 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9" s="49">
         <v>2020</v>
@@ -5429,13 +5417,13 @@
         <v>2019</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -5468,19 +5456,19 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10" s="49">
         <v>2020</v>
@@ -5490,13 +5478,13 @@
         <v>2019</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -5529,19 +5517,19 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G11" s="49">
         <v>2020</v>
@@ -5551,13 +5539,13 @@
         <v>2019</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -5590,19 +5578,19 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G12" s="49">
         <v>2020</v>
@@ -5612,13 +5600,13 @@
         <v>2019</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -5651,19 +5639,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13" s="49">
         <v>2020</v>
@@ -5673,13 +5661,13 @@
         <v>2019</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -5712,19 +5700,19 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G14" s="49">
         <v>2020</v>
@@ -5734,13 +5722,13 @@
         <v>2019</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -5773,19 +5761,19 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="49">
         <v>2020</v>
@@ -5795,13 +5783,13 @@
         <v>2019</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
@@ -5834,19 +5822,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" s="49">
         <v>2020</v>
@@ -5856,13 +5844,13 @@
         <v>2019</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -5895,19 +5883,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="49">
         <v>2020</v>
@@ -5917,13 +5905,13 @@
         <v>2019</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -5956,19 +5944,19 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G18" s="49">
         <v>2020</v>
@@ -5978,13 +5966,13 @@
         <v>2019</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -6017,19 +6005,19 @@
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G19" s="49">
         <v>2020</v>
@@ -6039,13 +6027,13 @@
         <v>2019</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -6078,19 +6066,19 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="49">
         <v>2020</v>
@@ -6100,13 +6088,13 @@
         <v>2019</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -6139,19 +6127,19 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="49">
         <v>2020</v>
@@ -6161,13 +6149,13 @@
         <v>2019</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -6200,19 +6188,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22" s="49">
         <v>2020</v>
@@ -6222,13 +6210,13 @@
         <v>2019</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -6261,19 +6249,19 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G23" s="49">
         <v>2020</v>
@@ -6283,13 +6271,13 @@
         <v>2019</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -6322,19 +6310,19 @@
         <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="49">
         <v>2020</v>
@@ -6344,13 +6332,13 @@
         <v>2019</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -6383,19 +6371,19 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G25" s="49">
         <v>2020</v>
@@ -6405,13 +6393,13 @@
         <v>2019</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -6456,4 +6444,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e4b931d8-a288-4db6-acc7-364bc8042050}" enabled="1" method="Privileged" siteId="{5218c2a1-81cc-40ce-af99-7505143bc263}" removed="0"/>
+</clbl:labelList>
 </file>